--- a/data/firms.xlsx
+++ b/data/firms.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MIDTERM_PROJECT\Team_2_FirmDataHub\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E007CF7B-B087-409C-8CA4-1E94615A6427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="10718" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,194 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="56">
+  <si>
+    <t>ticker</t>
+  </si>
+  <si>
+    <t>firm_id</t>
+  </si>
+  <si>
+    <t>company_name</t>
+  </si>
+  <si>
+    <t>founded_year</t>
+  </si>
+  <si>
+    <t>listed_year</t>
+  </si>
+  <si>
+    <t>BBC</t>
+  </si>
+  <si>
+    <t>CII</t>
+  </si>
+  <si>
+    <t>DBD</t>
+  </si>
+  <si>
+    <t>DMC</t>
+  </si>
+  <si>
+    <t>DPG</t>
+  </si>
+  <si>
+    <t>DQC</t>
+  </si>
+  <si>
+    <t>FCN</t>
+  </si>
+  <si>
+    <t>GSP</t>
+  </si>
+  <si>
+    <t>HHV</t>
+  </si>
+  <si>
+    <t>LSS</t>
+  </si>
+  <si>
+    <t>NSC</t>
+  </si>
+  <si>
+    <t>PDN</t>
+  </si>
+  <si>
+    <t>PHC</t>
+  </si>
+  <si>
+    <t>QNP</t>
+  </si>
+  <si>
+    <t>TCD</t>
+  </si>
+  <si>
+    <t>TLH</t>
+  </si>
+  <si>
+    <t>TMT</t>
+  </si>
+  <si>
+    <t>VIP</t>
+  </si>
+  <si>
+    <t>VNF</t>
+  </si>
+  <si>
+    <t>VNL</t>
+  </si>
+  <si>
+    <t>exchange_code</t>
+  </si>
+  <si>
+    <t>industry_l2_name</t>
+  </si>
+  <si>
+    <t>Bánh kẹo BIBICA</t>
+  </si>
+  <si>
+    <t>Hạ tầng Kỹ thuật TP.HCM</t>
+  </si>
+  <si>
+    <t>Dược - TB Y tế Bình Định</t>
+  </si>
+  <si>
+    <t>Dược phẩm DOMESCO</t>
+  </si>
+  <si>
+    <t>Tập đoàn Đạt Phương</t>
+  </si>
+  <si>
+    <t>Tập đoàn Điện Quang</t>
+  </si>
+  <si>
+    <t>FECON CORP</t>
+  </si>
+  <si>
+    <t>Vận tải Sản phẩm Khí Quốc tế</t>
+  </si>
+  <si>
+    <t>Đầu tư Hạ tầng Giao thông Đèo Cả</t>
+  </si>
+  <si>
+    <t>Mía đường Lam Sơn</t>
+  </si>
+  <si>
+    <t>Tập đoàn Giống cây trồng Việt Nam</t>
+  </si>
+  <si>
+    <t>Cảng Đồng Nai</t>
+  </si>
+  <si>
+    <t>Xây dựng Phục Hưng Holdings</t>
+  </si>
+  <si>
+    <t>Cảng Quy Nhơn</t>
+  </si>
+  <si>
+    <t>Tập đoàn Xây dựng Tracodi</t>
+  </si>
+  <si>
+    <t>Thép Tiến Lên</t>
+  </si>
+  <si>
+    <t>Ô tô TMT</t>
+  </si>
+  <si>
+    <t>Vận tải Xăng dầu VIPCO</t>
+  </si>
+  <si>
+    <t>VINAFREIGHT</t>
+  </si>
+  <si>
+    <t>Vinalink Logistics</t>
+  </si>
+  <si>
+    <t>HOSE</t>
+  </si>
+  <si>
+    <t>HNX</t>
+  </si>
+  <si>
+    <t>Thực phẩm và đồ uống</t>
+  </si>
+  <si>
+    <t>Xây dựng và Vật liệu</t>
+  </si>
+  <si>
+    <t>Y tế</t>
+  </si>
+  <si>
+    <t>Hàng cá nhân &amp; Gia dụng</t>
+  </si>
+  <si>
+    <t>Hàng &amp; Dịch vụ Công nghiệp</t>
+  </si>
+  <si>
+    <t>Tài nguyên Cơ bản</t>
+  </si>
+  <si>
+    <t>Ô tô và phụ tùng</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +234,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -330,10 +518,504 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.73046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.9296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1999</v>
+      </c>
+      <c r="G2" s="1">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3" s="1">
+        <v>2001</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1980</v>
+      </c>
+      <c r="G4" s="1">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5" s="1">
+        <v>1989</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2002</v>
+      </c>
+      <c r="G6" s="1">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1973</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2004</v>
+      </c>
+      <c r="G8" s="1">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2008</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="1">
+        <v>1974</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="1">
+        <v>1999</v>
+      </c>
+      <c r="G11" s="1">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1968</v>
+      </c>
+      <c r="G12" s="1">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="1">
+        <v>1989</v>
+      </c>
+      <c r="G13" s="1">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="1">
+        <v>2001</v>
+      </c>
+      <c r="G14" s="1">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="1">
+        <v>1976</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1990</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="1">
+        <v>1988</v>
+      </c>
+      <c r="G17" s="1">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" s="1">
+        <v>1976</v>
+      </c>
+      <c r="G18" s="1">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2005</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="1">
+        <v>1997</v>
+      </c>
+      <c r="G20" s="1">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F21" s="1">
+        <v>1999</v>
+      </c>
+      <c r="G21" s="1">
+        <v>2009</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>